--- a/todo.xlsx
+++ b/todo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gentoftehf-my.sharepoint.com/personal/hv_ghf_dk/Documents/GHF2/kemibog/kemic-web-2026/henryvest70.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A3EBA65-9A79-4CBF-959F-42F960362A9B}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EE7915D-9CCF-4DC7-89F5-40F5EA652D0C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AEC7298E-8AB4-4483-8A56-F40812FF3C99}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>forside</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>kemi b</t>
+  </si>
+  <si>
+    <t>kernebeg.</t>
+  </si>
+  <si>
+    <t>korr. Til 14.3</t>
   </si>
 </sst>
 </file>
@@ -551,6 +557,7 @@
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
       <c r="F1" s="2" t="s">
         <v>20</v>
       </c>
@@ -563,6 +570,9 @@
       <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="F2" t="s">
         <v>21</v>
       </c>
@@ -580,11 +590,14 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D3" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -595,6 +608,9 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
@@ -614,6 +630,9 @@
       <c r="C5" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="F5" t="s">
         <v>24</v>
       </c>
@@ -631,6 +650,9 @@
       <c r="C6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
@@ -648,6 +670,9 @@
       <c r="C7" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -659,6 +684,9 @@
       <c r="C8" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="F8" s="3" t="s">
         <v>25</v>
       </c>
@@ -671,7 +699,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
@@ -688,7 +719,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -699,7 +733,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -710,7 +747,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -721,7 +761,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -732,7 +775,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -743,7 +789,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -754,10 +803,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -767,8 +819,14 @@
       <c r="C17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -776,10 +834,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -787,7 +848,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gentoftehf-my.sharepoint.com/personal/hv_ghf_dk/Documents/GHF2/kemibog/kemic-web-2026/henryvest70.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EE7915D-9CCF-4DC7-89F5-40F5EA652D0C}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EBA490A-75BF-4313-8A3D-FF68E9DC5439}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AEC7298E-8AB4-4483-8A56-F40812FF3C99}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>forside</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>kernebeg.</t>
-  </si>
-  <si>
-    <t>korr. Til 14.3</t>
   </si>
 </sst>
 </file>
@@ -617,7 +614,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -809,24 +806,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -840,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>16</v>
       </c>

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gentoftehf-my.sharepoint.com/personal/hv_ghf_dk/Documents/GHF2/kemibog/kemic-web-2026/henryvest70.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EBA490A-75BF-4313-8A3D-FF68E9DC5439}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FAD8F54-A6C1-4A96-8615-1C97523AC70C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AEC7298E-8AB4-4483-8A56-F40812FF3C99}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>forside</t>
   </si>
@@ -116,13 +116,25 @@
     <t>henvisninger med kursiv</t>
   </si>
   <si>
-    <t>Andet</t>
-  </si>
-  <si>
-    <t>kemi b</t>
-  </si>
-  <si>
     <t>kernebeg.</t>
+  </si>
+  <si>
+    <t>Kemi B</t>
+  </si>
+  <si>
+    <t>estere</t>
+  </si>
+  <si>
+    <t>aminer</t>
+  </si>
+  <si>
+    <t>amider</t>
+  </si>
+  <si>
+    <t>syrechlorider</t>
+  </si>
+  <si>
+    <t>tom "basisk opløsning"</t>
   </si>
 </sst>
 </file>
@@ -542,13 +554,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F9B6C7-C649-488C-9048-3D989477E410}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -559,7 +571,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>17</v>
@@ -568,7 +580,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -577,7 +589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -597,7 +609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -617,7 +629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -636,8 +648,11 @@
       <c r="G5" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -657,7 +672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -671,7 +686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -685,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -702,13 +717,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -721,8 +736,14 @@
       <c r="D10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -735,8 +756,14 @@
       <c r="D11" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -749,8 +776,14 @@
       <c r="D12" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -764,7 +797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -778,7 +811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -792,7 +825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gentoftehf-my.sharepoint.com/personal/hv_ghf_dk/Documents/GHF2/kemibog/kemic-web-2026/henryvest70.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FAD8F54-A6C1-4A96-8615-1C97523AC70C}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{192FA592-E680-480F-942C-265EDB2AB49C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AEC7298E-8AB4-4483-8A56-F40812FF3C99}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>forside</t>
   </si>
@@ -134,7 +134,7 @@
     <t>syrechlorider</t>
   </si>
   <si>
-    <t>tom "basisk opløsning"</t>
+    <t>tom koefficient</t>
   </si>
 </sst>
 </file>
@@ -671,6 +671,9 @@
       <c r="G6" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -740,7 +743,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gentoftehf-my.sharepoint.com/personal/hv_ghf_dk/Documents/GHF2/kemibog/kemic-web-2026/henryvest70.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{192FA592-E680-480F-942C-265EDB2AB49C}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{BCA33B2C-D84F-4566-A23B-2D2B12BCD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A4D651F-5EDA-449C-97C0-FAFA21109F23}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AEC7298E-8AB4-4483-8A56-F40812FF3C99}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>forside</t>
   </si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>syrechlorider</t>
-  </si>
-  <si>
-    <t>tom koefficient</t>
   </si>
 </sst>
 </file>
@@ -554,13 +551,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F9B6C7-C649-488C-9048-3D989477E410}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -571,7 +568,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>17</v>
@@ -589,7 +586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -609,7 +606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -629,7 +626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -646,13 +643,10 @@
         <v>24</v>
       </c>
       <c r="G5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -669,13 +663,10 @@
         <v>18</v>
       </c>
       <c r="G6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -689,7 +680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -706,7 +697,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -726,7 +717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -746,7 +737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -763,10 +754,10 @@
         <v>29</v>
       </c>
       <c r="G11" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -783,10 +774,10 @@
         <v>30</v>
       </c>
       <c r="G12" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -800,7 +791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -814,7 +805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -828,7 +819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
